--- a/artfynd/A 18948-2023 artfynd.xlsx
+++ b/artfynd/A 18948-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18948-2023 artfynd.xlsx
+++ b/artfynd/A 18948-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,7 +3170,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112495174</v>
+        <v>112495166</v>
       </c>
       <c r="B25" t="n">
         <v>56513</v>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522448</v>
+        <v>522179</v>
       </c>
       <c r="R25" t="n">
-        <v>7077421</v>
+        <v>7077220</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,7 +3281,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112495166</v>
+        <v>112495172</v>
       </c>
       <c r="B26" t="n">
         <v>56513</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522179</v>
+        <v>522109</v>
       </c>
       <c r="R26" t="n">
-        <v>7077220</v>
+        <v>7077299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,7 +3392,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112495172</v>
+        <v>112495157</v>
       </c>
       <c r="B27" t="n">
         <v>56513</v>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522109</v>
+        <v>521286</v>
       </c>
       <c r="R27" t="n">
-        <v>7077299</v>
+        <v>7077616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112495157</v>
+        <v>112495179</v>
       </c>
       <c r="B28" t="n">
-        <v>56513</v>
+        <v>55732</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,42 +3515,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521286</v>
+        <v>522282</v>
       </c>
       <c r="R28" t="n">
-        <v>7077616</v>
+        <v>7077266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,11 +3579,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3614,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112495179</v>
+        <v>112495193</v>
       </c>
       <c r="B29" t="n">
-        <v>55732</v>
+        <v>90943</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3630,34 +3621,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522282</v>
+        <v>521385</v>
       </c>
       <c r="R29" t="n">
-        <v>7077266</v>
+        <v>7077670</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,6 +3692,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3716,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112495193</v>
+        <v>112495182</v>
       </c>
       <c r="B30" t="n">
-        <v>90943</v>
+        <v>90934</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3732,37 +3727,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521385</v>
+        <v>522424</v>
       </c>
       <c r="R30" t="n">
-        <v>7077670</v>
+        <v>7077374</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3803,7 +3795,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112495182</v>
+        <v>112495190</v>
       </c>
       <c r="B31" t="n">
-        <v>90934</v>
+        <v>89679</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3834,25 +3825,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3862,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522424</v>
+        <v>522469</v>
       </c>
       <c r="R31" t="n">
-        <v>7077374</v>
+        <v>7077316</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3921,108 +3912,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>112495190</v>
-      </c>
-      <c r="B32" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>holmflobackarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>522469</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7077316</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18948-2023 artfynd.xlsx
+++ b/artfynd/A 18948-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110263116</v>
+        <v>112495185</v>
       </c>
       <c r="B2" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1179</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupån, Jmt</t>
+          <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521541</v>
+        <v>522105</v>
       </c>
       <c r="R2" t="n">
-        <v>7077430</v>
+        <v>7077442</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112495170</v>
+        <v>112495187</v>
       </c>
       <c r="B3" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522164</v>
+        <v>522100</v>
       </c>
       <c r="R3" t="n">
-        <v>7077256</v>
+        <v>7077317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +872,7 @@
         <v>112495188</v>
       </c>
       <c r="B4" t="n">
-        <v>89657</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,53 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112495191</v>
+        <v>110263116</v>
       </c>
       <c r="B5" t="n">
-        <v>90907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>holmflobackarna, Jmt</t>
+          <t>Djupån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522424</v>
+        <v>521541</v>
       </c>
       <c r="R5" t="n">
-        <v>7077382</v>
+        <v>7077430</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,27 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim, Hugo Ström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112495185</v>
+        <v>112495191</v>
       </c>
       <c r="B6" t="n">
-        <v>89657</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522105</v>
+        <v>522424</v>
       </c>
       <c r="R6" t="n">
-        <v>7077442</v>
+        <v>7077382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112495180</v>
+        <v>112495182</v>
       </c>
       <c r="B7" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,37 +1172,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522427</v>
+        <v>522424</v>
       </c>
       <c r="R7" t="n">
-        <v>7077371</v>
+        <v>7077374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,9 +1238,8 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1301,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112495187</v>
+        <v>112495180</v>
       </c>
       <c r="B8" t="n">
-        <v>89657</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,34 +1269,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522100</v>
+        <v>522427</v>
       </c>
       <c r="R8" t="n">
-        <v>7077317</v>
+        <v>7077370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,8 +1338,9 @@
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112495176</v>
+        <v>112495193</v>
       </c>
       <c r="B9" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,27 +1370,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1447,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522488</v>
+        <v>521385</v>
       </c>
       <c r="R9" t="n">
-        <v>7077304</v>
+        <v>7077670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,17 +1435,13 @@
           <t>2023-10-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1514,15 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112495159</v>
+        <v>112495156</v>
       </c>
       <c r="B10" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521837</v>
+        <v>521387</v>
       </c>
       <c r="R10" t="n">
-        <v>7077579</v>
+        <v>7077693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112495165</v>
+        <v>112495157</v>
       </c>
       <c r="B11" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522086</v>
+        <v>521286</v>
       </c>
       <c r="R11" t="n">
-        <v>7077322</v>
+        <v>7077616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1645,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,15 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112495175</v>
+        <v>112495158</v>
       </c>
       <c r="B12" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522441</v>
+        <v>521432</v>
       </c>
       <c r="R12" t="n">
-        <v>7077389</v>
+        <v>7077482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112495167</v>
+        <v>112495159</v>
       </c>
       <c r="B13" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522205</v>
+        <v>521836</v>
       </c>
       <c r="R13" t="n">
-        <v>7077260</v>
+        <v>7077579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,15 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112495173</v>
+        <v>112495160</v>
       </c>
       <c r="B14" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522099</v>
+        <v>521847</v>
       </c>
       <c r="R14" t="n">
-        <v>7077313</v>
+        <v>7077543</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +1963,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,15 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112495158</v>
+        <v>112495162</v>
       </c>
       <c r="B15" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521432</v>
+        <v>522094</v>
       </c>
       <c r="R15" t="n">
-        <v>7077482</v>
+        <v>7077617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2069,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,12 +2099,7 @@
         <v>112495164</v>
       </c>
       <c r="B16" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2138,7 @@
         <v>522103</v>
       </c>
       <c r="R16" t="n">
-        <v>7077453</v>
+        <v>7077452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,15 +2202,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112495169</v>
+        <v>112495165</v>
       </c>
       <c r="B17" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2241,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522163</v>
+        <v>522087</v>
       </c>
       <c r="R17" t="n">
-        <v>7077259</v>
+        <v>7077322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2281,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,15 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112495156</v>
+        <v>112495166</v>
       </c>
       <c r="B18" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521387</v>
+        <v>522179</v>
       </c>
       <c r="R18" t="n">
-        <v>7077693</v>
+        <v>7077219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,15 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112495162</v>
+        <v>112495167</v>
       </c>
       <c r="B19" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>522094</v>
+        <v>522206</v>
       </c>
       <c r="R19" t="n">
-        <v>7077617</v>
+        <v>7077260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,7 +2493,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,15 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112495189</v>
+        <v>112495168</v>
       </c>
       <c r="B20" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,34 +2531,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>522081</v>
+        <v>522174</v>
       </c>
       <c r="R20" t="n">
-        <v>7077601</v>
+        <v>7077256</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,6 +2595,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,15 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112495171</v>
+        <v>112495169</v>
       </c>
       <c r="B21" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522120</v>
+        <v>522164</v>
       </c>
       <c r="R21" t="n">
-        <v>7077301</v>
+        <v>7077259</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,15 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112495168</v>
+        <v>112495170</v>
       </c>
       <c r="B22" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2881,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522175</v>
+        <v>522165</v>
       </c>
       <c r="R22" t="n">
-        <v>7077257</v>
+        <v>7077256</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,7 +2811,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,15 +2838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112495160</v>
+        <v>112495171</v>
       </c>
       <c r="B23" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521847</v>
+        <v>522120</v>
       </c>
       <c r="R23" t="n">
-        <v>7077543</v>
+        <v>7077301</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,15 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112495178</v>
+        <v>112495172</v>
       </c>
       <c r="B24" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522768</v>
+        <v>522109</v>
       </c>
       <c r="R24" t="n">
-        <v>7077362</v>
+        <v>7077299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,15 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112495166</v>
+        <v>112495173</v>
       </c>
       <c r="B25" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522179</v>
+        <v>522099</v>
       </c>
       <c r="R25" t="n">
-        <v>7077220</v>
+        <v>7077312</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,7 +3129,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,15 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112495172</v>
+        <v>112495174</v>
       </c>
       <c r="B26" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522109</v>
+        <v>522447</v>
       </c>
       <c r="R26" t="n">
-        <v>7077299</v>
+        <v>7077421</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,15 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112495157</v>
+        <v>112495175</v>
       </c>
       <c r="B27" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3436,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521286</v>
+        <v>522441</v>
       </c>
       <c r="R27" t="n">
-        <v>7077616</v>
+        <v>7077389</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,50 +3368,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112495179</v>
+        <v>112495176</v>
       </c>
       <c r="B28" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>holmflobackarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522282</v>
+        <v>522488</v>
       </c>
       <c r="R28" t="n">
-        <v>7077266</v>
+        <v>7077304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3579,6 +3443,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3605,42 +3474,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112495193</v>
+        <v>112495178</v>
       </c>
       <c r="B29" t="n">
-        <v>90943</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3648,10 +3513,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521385</v>
+        <v>522768</v>
       </c>
       <c r="R29" t="n">
-        <v>7077670</v>
+        <v>7077362</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,13 +3551,17 @@
           <t>2023-10-02</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3711,15 +3580,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112495182</v>
+        <v>112495179</v>
       </c>
       <c r="B30" t="n">
-        <v>90934</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,21 +3591,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3751,10 +3615,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522424</v>
+        <v>522283</v>
       </c>
       <c r="R30" t="n">
-        <v>7077374</v>
+        <v>7077266</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,108 +3674,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>112495190</v>
-      </c>
-      <c r="B31" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>holmflobackarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>522469</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7077316</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18948-2023 artfynd.xlsx
+++ b/artfynd/A 18948-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495187</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495188</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110263116</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495191</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495182</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495180</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495193</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495156</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495157</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495158</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495159</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495160</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495162</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2199,6 +2274,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495164</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495165</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495166</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495167</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495168</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495169</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495170</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495171</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495172</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3153,6 +3273,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495173</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3384,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495174</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3365,6 +3495,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495175</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3471,6 +3606,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495176</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3577,6 +3717,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495178</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3674,8 +3819,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>